--- a/artfynd/A 51706-2024 artfynd.xlsx
+++ b/artfynd/A 51706-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>66548562</v>
       </c>
       <c r="B2" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561864.3780827143</v>
+        <v>561864</v>
       </c>
       <c r="R2" t="n">
-        <v>7230793.001096533</v>
+        <v>7230793</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66548560</v>
+        <v>66548561</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hudmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561986.7692078566</v>
+        <v>561928</v>
       </c>
       <c r="R3" t="n">
-        <v>7230773.719095272</v>
+        <v>7230823</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +849,9 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66548561</v>
+        <v>66548560</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,38 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hudmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561928.1095514798</v>
+        <v>561987</v>
       </c>
       <c r="R4" t="n">
-        <v>7230822.906127009</v>
+        <v>7230774</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +951,9 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +967,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>26941</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1027,123 +982,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>66548559</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Hudmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>561957.1389648776</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7230742.42656224</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>26939</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
